--- a/public/modelos/larume-modelo-importacao.xlsx
+++ b/public/modelos/larume-modelo-importacao.xlsx
@@ -137,7 +137,7 @@
     <t>Obrigatória?</t>
   </si>
   <si>
-    <t>Nome do item. Até 200 caracteres.</t>
+    <t>Nome do item. Até 36 caracteres.</t>
   </si>
   <si>
     <t>Sim</t>
